--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>会计员/注册会计师</t>
+          <t>助理会计师</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">

--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,6 +608,16 @@
           <t>联系方式</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>状态详情</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -658,6 +668,12 @@
           <t>17636671760</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -708,6 +724,12 @@
           <t>13980885726</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -758,6 +780,12 @@
           <t>18382194536</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -808,6 +836,12 @@
           <t>18523176628</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -858,6 +892,12 @@
           <t>13983081015</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -908,6 +948,12 @@
           <t>15663629810</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -958,6 +1004,12 @@
           <t>15308505399</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1009,6 +1061,12 @@
           <t>17339909941</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1059,6 +1117,12 @@
           <t>18850446530</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -1109,6 +1173,12 @@
           <t>18152025132</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1159,6 +1229,12 @@
           <t>17635108453</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1209,6 +1285,12 @@
           <t>18822581330</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1259,6 +1341,12 @@
           <t>13155825161</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1309,6 +1397,12 @@
           <t>15196251135</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1359,6 +1453,12 @@
           <t>13289979599</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1409,6 +1509,12 @@
           <t>13688220125</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1460,6 +1566,12 @@
           <t>13662658688</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1510,6 +1622,12 @@
           <t>18308460605</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1560,6 +1678,12 @@
           <t>13808060102</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1610,6 +1734,12 @@
           <t>19922757080</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1660,6 +1790,12 @@
           <t>19985148542</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1706,6 +1842,12 @@
           <t>13910232610</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1756,6 +1898,12 @@
           <t>15756305065</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1806,6 +1954,12 @@
           <t>15828600451</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1856,6 +2010,12 @@
           <t>18423545580</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1906,6 +2066,12 @@
           <t>13110520513</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -1956,6 +2122,12 @@
           <t>15268994084</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -2006,6 +2178,12 @@
           <t>15121627755</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -2056,6 +2234,12 @@
           <t>13982680413</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2107,6 +2291,12 @@
           <t>15735103522</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2157,6 +2347,12 @@
           <t>17585409552</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2207,6 +2403,12 @@
           <t>18281601467</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2253,6 +2455,12 @@
           <t>18501960916</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -2304,6 +2512,12 @@
           <t>17336334413</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2354,6 +2568,12 @@
           <t>13678286928</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -2405,6 +2625,12 @@
           <t>13098592845</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2455,6 +2681,12 @@
           <t>19103129717</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2505,6 +2737,12 @@
           <t>15680488189</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2555,6 +2793,12 @@
           <t>15611017000</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2605,6 +2849,12 @@
           <t>18782744825</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2655,6 +2905,12 @@
           <t>13934523393</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -2705,6 +2961,12 @@
           <t>18080157008</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -2755,6 +3017,12 @@
           <t>19722755593</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -2805,6 +3073,12 @@
           <t>18886074997</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -2855,6 +3129,12 @@
           <t>15776586527</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -2905,6 +3185,12 @@
           <t>17585372839</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2955,6 +3241,12 @@
           <t>15121651375</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -3006,6 +3298,12 @@
           <t>17839942039</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -3056,6 +3354,12 @@
           <t>13880815368</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -3106,6 +3410,12 @@
           <t>18744778892</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3158,6 +3468,12 @@
           <t>18100820067</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -3208,6 +3524,12 @@
           <t>15808500870</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3258,6 +3580,12 @@
           <t>18585071104</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3308,6 +3636,12 @@
           <t>18788795304</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -3358,6 +3692,12 @@
           <t>15982001023</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -3408,6 +3748,12 @@
           <t>18875096025</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -3458,6 +3804,12 @@
           <t>18910719354</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -3508,6 +3860,12 @@
           <t>18100820067</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -3559,6 +3917,12 @@
           <t>13370754597</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -3609,6 +3973,12 @@
           <t>13934523393</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -3659,6 +4029,12 @@
           <t>17720798719</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3674,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3753,6 +4129,16 @@
           <t>联系方式</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>状态详情</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -3823,6 +4209,12 @@
           <t>13696275089</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -3876,6 +4268,12 @@
           <t>13079261723</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -3929,6 +4327,12 @@
           <t>18581898039</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -3982,6 +4386,12 @@
           <t>15545185655</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -4035,6 +4445,12 @@
           <t>13996282264</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -4088,6 +4504,12 @@
           <t>13883302580</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -4141,6 +4563,12 @@
           <t>17528106086</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -4194,6 +4622,12 @@
           <t>18298342660</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -4247,6 +4681,12 @@
           <t>17349851045</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -4300,6 +4740,12 @@
           <t>15680137005</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -4353,6 +4799,12 @@
           <t>19832232517</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -4406,6 +4858,12 @@
           <t>18601303170</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -4459,6 +4917,12 @@
           <t>13890159216</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -4512,6 +4976,12 @@
           <t>18280196306</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -4565,6 +5035,12 @@
           <t>18281157735</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -4618,6 +5094,12 @@
           <t>15545185655</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -4671,6 +5153,12 @@
           <t>13696275089</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -4724,6 +5212,12 @@
           <t>18672949006</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -4773,6 +5267,12 @@
           <t>18398711177</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -4839,6 +5339,12 @@
           <t>17366926256</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -4892,6 +5398,12 @@
           <t>18903490870</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -4945,6 +5457,12 @@
           <t>15883780723</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -4998,6 +5516,12 @@
           <t>18328280220</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -5051,6 +5575,12 @@
           <t>17318686006</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -5104,6 +5634,12 @@
           <t>13693455686</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -5157,6 +5693,12 @@
           <t>18982270091</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -5210,6 +5752,12 @@
           <t>18685001409</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -5263,6 +5811,12 @@
           <t>13688248308</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -5316,6 +5870,12 @@
           <t>18109050421</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -5369,6 +5929,12 @@
           <t>15928415362</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -5422,6 +5988,12 @@
           <t>15208110473</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -5475,6 +6047,12 @@
           <t>18582993354</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -5528,6 +6106,12 @@
           <t>17318977128</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -5581,6 +6165,12 @@
           <t>15802801598</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -5634,6 +6224,12 @@
           <t>18473711688</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -5687,6 +6283,12 @@
           <t>18328416652</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -5740,6 +6342,12 @@
           <t>17783097813</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -5793,6 +6401,12 @@
           <t>13378102918</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -5846,6 +6460,12 @@
           <t>18483667007</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -5899,6 +6519,12 @@
           <t>18349348159</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -5952,6 +6578,12 @@
           <t>15910353201</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -6005,6 +6637,12 @@
           <t>18482144856</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -6058,6 +6696,12 @@
           <t>15213702202</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -6111,6 +6755,12 @@
           <t>13765499358</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -6164,6 +6814,12 @@
           <t>15520090613</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -6217,6 +6873,12 @@
           <t>13547752670</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -6270,6 +6932,12 @@
           <t>15196642169</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -6323,6 +6991,12 @@
           <t>19936232937</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>在岗</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -673,7 +673,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -729,7 +728,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -785,7 +783,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -841,7 +838,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -897,7 +893,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -953,7 +948,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1009,7 +1003,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1066,7 +1059,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1122,7 +1114,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -1178,7 +1169,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1234,7 +1224,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1290,7 +1279,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1346,7 +1334,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1402,7 +1389,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1458,7 +1444,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1514,7 +1499,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1571,7 +1555,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1627,7 +1610,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1683,7 +1665,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1739,7 +1720,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1795,7 +1775,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1847,7 +1826,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1903,7 +1881,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1959,7 +1936,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -2015,7 +1991,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -2071,7 +2046,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -2127,7 +2101,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -2183,7 +2156,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -2239,7 +2211,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2296,7 +2267,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2352,7 +2322,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2408,7 +2377,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2460,7 +2428,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -2517,7 +2484,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2573,7 +2539,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -2630,7 +2595,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2686,7 +2650,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2742,7 +2705,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2798,7 +2760,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2854,7 +2815,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2910,7 +2870,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -2966,7 +2925,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -3022,7 +2980,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -3078,7 +3035,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -3134,7 +3090,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -3190,7 +3145,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -3246,7 +3200,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -3303,7 +3256,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -3359,7 +3311,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -3415,7 +3366,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3473,7 +3423,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -3529,7 +3478,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3572,7 +3520,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>遂宁站</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -3585,7 +3533,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3641,7 +3588,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -3697,7 +3643,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -3753,7 +3698,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -3809,7 +3753,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -3865,7 +3808,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -3922,7 +3864,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -3978,7 +3919,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -4034,7 +3974,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4209,12 +4148,16 @@
           <t>13696275089</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>崇州片区</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -4268,12 +4211,16 @@
           <t>13079261723</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -4327,12 +4274,16 @@
           <t>18581898039</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>大足站</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -4386,12 +4337,16 @@
           <t>15545185655</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>凤凰山</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -4445,12 +4400,16 @@
           <t>13996282264</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>成达万</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -4509,7 +4468,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -4563,12 +4521,16 @@
           <t>17528106086</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>红星路</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -4622,12 +4584,16 @@
           <t>18298342660</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -4681,12 +4647,16 @@
           <t>17349851045</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>大足站</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -4740,12 +4710,16 @@
           <t>15680137005</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>西南交大</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -4799,12 +4773,16 @@
           <t>19832232517</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -4863,7 +4841,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -4917,12 +4894,16 @@
           <t>13890159216</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -4976,12 +4957,16 @@
           <t>18280196306</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -5035,12 +5020,16 @@
           <t>18281157735</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -5094,12 +5083,16 @@
           <t>15545185655</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -5153,12 +5146,16 @@
           <t>13696275089</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>西南交大</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -5212,12 +5209,16 @@
           <t>18672949006</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -5267,12 +5268,16 @@
           <t>18398711177</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>川南片区</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -5339,12 +5344,16 @@
           <t>17366926256</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>成达万</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -5398,12 +5407,16 @@
           <t>18903490870</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -5457,12 +5470,16 @@
           <t>15883780723</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -5516,12 +5533,16 @@
           <t>18328280220</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -5575,12 +5596,16 @@
           <t>17318686006</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -5634,12 +5659,16 @@
           <t>13693455686</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>大足站</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -5698,7 +5727,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -5752,12 +5780,16 @@
           <t>18685001409</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -5811,12 +5843,16 @@
           <t>13688248308</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -5870,12 +5906,16 @@
           <t>18109050421</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -5929,12 +5969,16 @@
           <t>15928415362</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -5988,12 +6032,16 @@
           <t>15208110473</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -6047,12 +6095,16 @@
           <t>18582993354</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -6106,12 +6158,16 @@
           <t>17318977128</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -6165,12 +6221,16 @@
           <t>15802801598</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -6224,12 +6284,16 @@
           <t>18473711688</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>成达万</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -6283,12 +6347,16 @@
           <t>18328416652</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -6342,12 +6410,16 @@
           <t>17783097813</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -6401,12 +6473,16 @@
           <t>13378102918</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -6460,12 +6536,16 @@
           <t>18483667007</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -6519,12 +6599,16 @@
           <t>18349348159</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>后台</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -6578,12 +6662,16 @@
           <t>15910353201</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>马厂坝</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -6637,12 +6725,16 @@
           <t>18482144856</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -6696,12 +6788,16 @@
           <t>15213702202</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -6760,7 +6856,6 @@
           <t>在岗</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -6814,12 +6909,16 @@
           <t>15520090613</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -6873,12 +6972,16 @@
           <t>13547752670</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>成都北站</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -6932,12 +7035,16 @@
           <t>15196642169</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>红星路</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -6991,12 +7098,16 @@
           <t>19936232937</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>成都北站</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4463,6 +4463,11 @@
           <t>13883302580</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>西南交大片区</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>在岗</t>
@@ -4834,6 +4839,11 @@
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>18601303170</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>其他</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -5298,7 +5308,7 @@
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -5357,7 +5367,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
@@ -5420,7 +5430,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -5483,7 +5493,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
@@ -5546,7 +5556,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
@@ -5609,7 +5619,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
@@ -5672,11 +5682,11 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>岳巍</t>
+          <t>张伦勇</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -5686,12 +5696,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>513722198311295412</t>
+          <t>522101198406137018</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1983.11</t>
+          <t>1984年6月</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -5701,12 +5711,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>四川成都</t>
+          <t>贵州遵义</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>施工员</t>
+          <t>消防测试</t>
         </is>
       </c>
       <c r="I30" s="5" t="n">
@@ -5714,12 +5724,17 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>6.30离职</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>18982270091</t>
+          <t>18685001409</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>成都北站</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5730,11 +5745,11 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>张伦勇</t>
+          <t>张家驹</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5744,31 +5759,31 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>522101198406137018</t>
+          <t>51112219970514019X</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>1984年6月</t>
+          <t>1997年5月</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>贵州遵义</t>
+          <t>四川省眉山市</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>消防测试</t>
+          <t>BIM岗</t>
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>9000</v>
+        <v>8500</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
@@ -5777,12 +5792,12 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>18685001409</t>
+          <t>13688248308</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>成都北站</t>
+          <t>遂宁站</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5793,45 +5808,45 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>张家驹</t>
+          <t>张烨帆</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>51112219970514019X</t>
+          <t>131182199804215420</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>1997年5月</t>
+          <t>1998.04</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>专科</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>四川省眉山市</t>
+          <t>四川成都</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>BIM岗</t>
+          <t>资料员</t>
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>8500</v>
+        <v>5000</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -5840,12 +5855,12 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>13688248308</t>
+          <t>18109050421</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>遂宁站</t>
+          <t>后台</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5856,11 +5871,11 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>张烨帆</t>
+          <t>彭宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5870,17 +5885,17 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>131182199804215420</t>
+          <t>510122199508061926</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1998.04</t>
+          <t>1995.08</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -5890,11 +5905,11 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>资料员</t>
+          <t>班组长</t>
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
@@ -5903,7 +5918,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>18109050421</t>
+          <t>15928415362</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5919,26 +5934,26 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>彭宁</t>
+          <t>朱荣</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>510122199508061926</t>
+          <t>411321198808030918</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>1995.08</t>
+          <t>1998年8月</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -5948,16 +5963,16 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>四川成都</t>
+          <t>四川雅安</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>班组长</t>
+          <t>BIM</t>
         </is>
       </c>
       <c r="I34" s="5" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -5966,7 +5981,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>15928415362</t>
+          <t>15208110473</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5982,36 +5997,36 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>朱荣</t>
+          <t>李宣霖</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>411321198808030918</t>
+          <t>510121199802048427</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1998年8月</t>
+          <t>1998年2月</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>专科</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>四川雅安</t>
+          <t>四川金堂</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -6020,7 +6035,7 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -6029,7 +6044,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>15208110473</t>
+          <t>18582993354</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -6045,26 +6060,26 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>李宣霖</t>
+          <t>杨天祥</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>510121199802048427</t>
+          <t>513902200302237590</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1998年2月</t>
+          <t>2003年2月</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -6074,7 +6089,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>四川金堂</t>
+          <t>成都简阳</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -6083,7 +6098,7 @@
         </is>
       </c>
       <c r="I36" s="5" t="n">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
@@ -6092,7 +6107,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>18582993354</t>
+          <t>17318977128</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -6108,11 +6123,11 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>杨天祥</t>
+          <t>林贵春</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -6122,12 +6137,12 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>513902200302237590</t>
+          <t>510902197903191973</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2003年2月</t>
+          <t>1979年3月</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -6137,16 +6152,16 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>成都简阳</t>
+          <t>四川省遂宁市</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>BIM</t>
+          <t>电气设计</t>
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
@@ -6155,7 +6170,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>17318977128</t>
+          <t>15802801598</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -6171,11 +6186,11 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>林贵春</t>
+          <t>殷尚明</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -6185,31 +6200,31 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>510902197903191973</t>
+          <t>43090319801207271X</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>1979年3月</t>
+          <t>1980-12-07</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>大专</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>四川省遂宁市</t>
+          <t xml:space="preserve">湖南益阳 </t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>电气设计</t>
+          <t>施工员</t>
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -6218,12 +6233,12 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>15802801598</t>
+          <t>18473711688</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>后台</t>
+          <t>成达万</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6234,45 +6249,45 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>殷尚明</t>
+          <t>王茂霞</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>43090319801207271X</t>
+          <t>510823199605167428</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>1980-12-07</t>
+          <t>1996.5</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>大专</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">湖南益阳 </t>
+          <t>四川省广元</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>施工员</t>
+          <t>预算员/助理工程师</t>
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>9000</v>
+        <v>8500</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -6281,12 +6296,12 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>18473711688</t>
+          <t>18328416652</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>成达万</t>
+          <t>后台</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6297,26 +6312,26 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>王茂霞</t>
+          <t>程实</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>510823199605167428</t>
+          <t>342601198510126291</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1996.5</t>
+          <t>1985-10-12</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -6326,16 +6341,16 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>四川省广元</t>
+          <t>安徽省合肥市</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>预算员/助理工程师</t>
+          <t>司机</t>
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>8500</v>
+        <v>6500</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -6344,7 +6359,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>18328416652</t>
+          <t>17783097813</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -6360,11 +6375,11 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>程实</t>
+          <t>罗可</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -6374,12 +6389,12 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>342601198510126291</t>
+          <t>511321199203055950</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1985-10-12</t>
+          <t>1992.03</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -6389,16 +6404,16 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>安徽省合肥市</t>
+          <t>四川南充</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>司机</t>
+          <t>给排水设计</t>
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>6500</v>
+        <v>10000</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -6407,7 +6422,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>17783097813</t>
+          <t>13378102918</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -6423,26 +6438,26 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>罗可</t>
+          <t>胡薇佳</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>511321199203055950</t>
+          <t>511323199511290023</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>1992.03</t>
+          <t>1995.11</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -6452,12 +6467,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>四川南充</t>
+          <t>四川蓬安</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>给排水设计</t>
+          <t>班组长</t>
         </is>
       </c>
       <c r="I42" s="5" t="n">
@@ -6470,7 +6485,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>13378102918</t>
+          <t>18483667007</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -6486,11 +6501,11 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>胡薇佳</t>
+          <t>蒋艾伶</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -6500,12 +6515,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>511323199511290023</t>
+          <t>513922199303260303</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>1995.11</t>
+          <t>1993.03</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -6515,16 +6530,16 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>四川蓬安</t>
+          <t>四川省乐至</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>班组长</t>
+          <t>预算员</t>
         </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>10000</v>
+        <v>8500</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -6533,7 +6548,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>18483667007</t>
+          <t>18349348159</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -6549,26 +6564,26 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>蒋艾伶</t>
+          <t>谷阳盆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>513922199303260303</t>
+          <t>430482200303191098</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1993.03</t>
+          <t>2003.03</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -6578,16 +6593,16 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>四川省乐至</t>
+          <t>湖南衡阳</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>预算员</t>
+          <t>施工员</t>
         </is>
       </c>
       <c r="I44" s="5" t="n">
-        <v>8500</v>
+        <v>5400</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -6596,12 +6611,12 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>18349348159</t>
+          <t>15910353201</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>后台</t>
+          <t>马厂坝</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6612,26 +6627,26 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>谷阳盆</t>
+          <t>赵彬君</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>430482200303191098</t>
+          <t>510402199604255924</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2003.03</t>
+          <t>1996.04</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -6641,16 +6656,16 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>湖南衡阳</t>
+          <t>四川攀枝花</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>施工员</t>
+          <t>安装造价员</t>
         </is>
       </c>
       <c r="I45" s="5" t="n">
-        <v>5400</v>
+        <v>9000</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -6659,12 +6674,12 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>15910353201</t>
+          <t>18482144856</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>马厂坝</t>
+          <t>成都北站</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6675,45 +6690,45 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>赵彬君</t>
+          <t>邹正林</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>510402199604255924</t>
+          <t>500230199909291574</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>1996.04</t>
+          <t>1999.09</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>专科</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>四川攀枝花</t>
+          <t>重庆丰都</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>安装造价员</t>
+          <t>安全员</t>
         </is>
       </c>
       <c r="I46" s="5" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -6722,12 +6737,12 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>18482144856</t>
+          <t>15213702202</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>成都北站</t>
+          <t>遂宁站</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6738,11 +6753,11 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>邹正林</t>
+          <t>郎国鹏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -6752,31 +6767,31 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>500230199909291574</t>
+          <t>522723200108253310</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>1999.09</t>
+          <t>2001.08</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>重庆丰都</t>
+          <t>贵州贵定</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>安全员</t>
+          <t>技术员</t>
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>7000</v>
+        <v>5360</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -6785,12 +6800,12 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>15213702202</t>
+          <t>13765499358</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>遂宁站</t>
+          <t>贵州片区</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6801,45 +6816,45 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>郎国鹏</t>
+          <t>陈垚</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>522723200108253310</t>
+          <t>500233200206134227</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2001.08</t>
+          <t>2002年6月</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>专科</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>贵州贵定</t>
+          <t>重庆忠县</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>技术员</t>
+          <t>资料员</t>
         </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>5360</v>
+        <v>6000</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -6848,7 +6863,12 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>13765499358</t>
+          <t>15520090613</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>遂宁站</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6859,45 +6879,45 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>陈垚</t>
+          <t>陈洪春</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>500233200206134227</t>
+          <t>510902198912096534</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2002年6月</t>
+          <t>1989.12</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>重庆忠县</t>
+          <t>四川遂宁</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>资料员</t>
+          <t>施工员</t>
         </is>
       </c>
       <c r="I49" s="5" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
@@ -6906,12 +6926,12 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>15520090613</t>
+          <t>13547752670</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>遂宁站</t>
+          <t>成都北站</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6922,11 +6942,11 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>陈洪春</t>
+          <t>顾清勇</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -6936,22 +6956,22 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>510902198912096534</t>
+          <t>513901198608084156</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>1989.12</t>
+          <t>1986.08</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>四川遂宁</t>
+          <t>四川成都</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -6960,7 +6980,7 @@
         </is>
       </c>
       <c r="I50" s="5" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -6969,12 +6989,12 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>13547752670</t>
+          <t>15196642169</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>成都北站</t>
+          <t>红星路</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6985,11 +7005,11 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>顾清勇</t>
+          <t>马宏伟</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -6999,31 +7019,31 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>513901198608084156</t>
+          <t>500240198611200156</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1986.08</t>
+          <t>1986.11</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>初中</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>四川成都</t>
+          <t>重庆石柱</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>施工员</t>
+          <t>班组长</t>
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>10000</v>
+        <v>9500</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
@@ -7032,78 +7052,15 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>15196642169</t>
+          <t>19936232937</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>红星路</t>
+          <t>遂宁站</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
-        <is>
-          <t>在岗</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>马宏伟</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>500240198611200156</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>1986.11</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>重庆石柱</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>班组长</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>19936232937</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>遂宁站</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
         <is>
           <t>在岗</t>
         </is>

--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -4465,7 +4465,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>西南交大片区</t>
+          <t>西南交大</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">

--- a/data/安装公司最新人员花名册.xlsx
+++ b/data/安装公司最新人员花名册.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>助理会计师</t>
+          <t>会计员/助理会计师</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>班组长</t>
+          <t>暖通设计师</t>
         </is>
       </c>
       <c r="I33" s="5" t="n">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>班组长</t>
+          <t>电气设计师</t>
         </is>
       </c>
       <c r="I42" s="5" t="n">
